--- a/templates/deliverable/example/02_테이블정의서.xlsx
+++ b/templates/deliverable/example/02_테이블정의서.xlsx
@@ -12,39 +12,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>테이블 정의서</t>
   </si>
   <si>
+    <t>영문 DB명</t>
+  </si>
+  <si>
+    <t>테이블 소유자</t>
+  </si>
+  <si>
+    <t>한글 테이블명</t>
+  </si>
+  <si>
+    <t>영문 테이블명</t>
+  </si>
+  <si>
+    <t>테이블 유형</t>
+  </si>
+  <si>
+    <t>관련 엔터티명</t>
+  </si>
+  <si>
+    <t>테이블 설명</t>
+  </si>
+  <si>
+    <t>발생주기</t>
+  </si>
+  <si>
+    <t>테이블 볼륨</t>
+  </si>
+  <si>
+    <t>공개/비공개 여부</t>
+  </si>
+  <si>
+    <t>개방데이터목록</t>
+  </si>
+  <si>
     <t>순번</t>
   </si>
   <si>
-    <t>테이블소유자</t>
-  </si>
-  <si>
-    <t>테이블명(영문)</t>
-  </si>
-  <si>
-    <t>테이블명(한글)</t>
-  </si>
-  <si>
-    <t>테이블용도</t>
-  </si>
-  <si>
-    <t>관련엔터티명</t>
-  </si>
-  <si>
-    <t>테이블설명</t>
-  </si>
-  <si>
     <t>보존기간</t>
-  </si>
-  <si>
-    <t>갱신주기</t>
-  </si>
-  <si>
-    <t>테이블볼륨(건)</t>
   </si>
   <si>
     <t>예상발생량(건)</t>
@@ -89,12 +98,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -148,8 +157,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -157,28 +166,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.0" customWidth="true"/>
-    <col min="2" max="2" width="16.0" customWidth="true"/>
-    <col min="3" max="3" width="20.0" customWidth="true"/>
-    <col min="4" max="4" width="20.0" customWidth="true"/>
-    <col min="5" max="5" width="14.0" customWidth="true"/>
-    <col min="6" max="6" width="16.0" customWidth="true"/>
-    <col min="7" max="7" width="14.0" customWidth="true"/>
+    <col min="1" max="1" width="16.0" customWidth="true"/>
+    <col min="2" max="2" width="18.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="5" max="5" width="16.0" customWidth="true"/>
+    <col min="6" max="6" width="18.0" customWidth="true"/>
+    <col min="7" max="7" width="16.0" customWidth="true"/>
     <col min="8" max="8" width="12.0" customWidth="true"/>
-    <col min="9" max="9" width="12.0" customWidth="true"/>
-    <col min="10" max="10" width="20.0" customWidth="true"/>
-    <col min="11" max="11" width="20.0" customWidth="true"/>
-    <col min="12" max="12" width="10.0" customWidth="true"/>
+    <col min="9" max="9" width="16.0" customWidth="true"/>
+    <col min="10" max="10" width="22.0" customWidth="true"/>
+    <col min="11" max="11" width="18.0" customWidth="true"/>
+    <col min="12" max="12" width="8.0" customWidth="true"/>
     <col min="13" max="13" width="12.0" customWidth="true"/>
-    <col min="14" max="14" width="12.0" customWidth="true"/>
+    <col min="14" max="14" width="20.0" customWidth="true"/>
     <col min="15" max="15" width="10.0" customWidth="true"/>
-    <col min="16" max="16" width="14.0" customWidth="true"/>
-    <col min="17" max="17" width="14.0" customWidth="true"/>
-    <col min="18" max="18" width="14.0" customWidth="true"/>
-    <col min="19" max="19" width="12.0" customWidth="true"/>
+    <col min="16" max="16" width="12.0" customWidth="true"/>
+    <col min="17" max="17" width="12.0" customWidth="true"/>
+    <col min="18" max="18" width="10.0" customWidth="true"/>
+    <col min="19" max="19" width="14.0" customWidth="true"/>
+    <col min="20" max="20" width="14.0" customWidth="true"/>
+    <col min="21" max="21" width="14.0" customWidth="true"/>
+    <col min="22" max="22" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -243,6 +255,15 @@
       </c>
       <c r="S2" t="s" s="2">
         <v>19</v>
+      </c>
+      <c r="T2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V2" t="s" s="2">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -265,6 +286,9 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
